--- a/results/tables/表3_优化前后多指标对比.xlsx
+++ b/results/tables/表3_优化前后多指标对比.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>98.7</t>
         </is>
       </c>
     </row>
@@ -487,12 +487,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0028</t>
+          <t>0.0002</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0004</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>69.6</t>
         </is>
       </c>
     </row>

--- a/results/tables/表3_优化前后多指标对比.xlsx
+++ b/results/tables/表3_优化前后多指标对比.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>99.1</t>
         </is>
       </c>
     </row>
@@ -487,12 +487,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0002</t>
+          <t>0.0036</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0044</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>178.4</t>
         </is>
       </c>
     </row>

--- a/results/tables/表3_优化前后多指标对比.xlsx
+++ b/results/tables/表3_优化前后多指标对比.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.3</t>
         </is>
       </c>
     </row>
@@ -487,12 +487,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.0029</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>178.4</t>
+          <t>199.6</t>
         </is>
       </c>
     </row>
